--- a/results/att_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
+++ b/results/att_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
@@ -534,13 +534,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.045</v>
+        <v>0.012</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.002</v>
+        <v>0.003</v>
       </c>
       <c r="E4" t="n">
-        <v>0.043</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.061</v>
+        <v>0.046</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.057</v>
+        <v>0.045</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -672,7 +672,7 @@
         <v>-0.008999999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0.008999999999999999</v>
@@ -699,10 +699,10 @@
         <v>-0.074</v>
       </c>
       <c r="D10" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="E10" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -726,10 +726,10 @@
         <v>0.034</v>
       </c>
       <c r="D11" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="E11" t="n">
-        <v>0.032</v>
+        <v>0.033</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -807,10 +807,10 @@
         <v>0.041</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.008</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>0.033</v>
+        <v>0.032</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -834,10 +834,10 @@
         <v>0.005</v>
       </c>
       <c r="D15" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -861,10 +861,10 @@
         <v>0.032</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.005</v>
+        <v>-0.004</v>
       </c>
       <c r="E16" t="n">
-        <v>0.027</v>
+        <v>0.028</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -888,10 +888,10 @@
         <v>-0.014</v>
       </c>
       <c r="D17" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="E17" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -915,10 +915,10 @@
         <v>-0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -969,10 +969,10 @@
         <v>0.077</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="E20" t="n">
-        <v>0.075</v>
+        <v>0.076</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -996,10 +996,10 @@
         <v>-0.019</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.001</v>
+        <v>-0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1131,10 +1131,10 @@
         <v>-0.128</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.003</v>
+        <v>-0.002</v>
       </c>
       <c r="E26" t="n">
-        <v>0.125</v>
+        <v>0.126</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
@@ -1266,10 +1266,10 @@
         <v>-0.041</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.001</v>
+        <v>-0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.04</v>
+        <v>0.041</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -1293,10 +1293,10 @@
         <v>-0.066</v>
       </c>
       <c r="D32" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="E32" t="n">
-        <v>0.06</v>
+        <v>0.059</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1388,13 +1388,13 @@
         <v>7220</v>
       </c>
       <c r="B2" t="n">
-        <v>554.8407173044708</v>
+        <v>554.8319074166568</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07201647252918561</v>
+        <v>0.07201588164977409</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2496220969064754</v>
+        <v>0.2496221955703657</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -1464,19 +1464,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.195531518251576</v>
+        <v>2.236944464107627</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3521744673774248</v>
+        <v>0.3384250196146405</v>
       </c>
       <c r="D2" t="n">
-        <v>1.505282245917247</v>
+        <v>1.57364361419567</v>
       </c>
       <c r="E2" t="n">
-        <v>2.885780790585905</v>
+        <v>2.900245314019584</v>
       </c>
       <c r="F2" t="n">
-        <v>4.540477243496419e-10</v>
+        <v>3.846647276145911e-11</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1828025524369364</v>
+        <v>0.181150802664234</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06434018447999743</v>
+        <v>0.06590363351848993</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05669810809747855</v>
+        <v>0.05198205451766702</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3089069967763943</v>
+        <v>0.310319550810801</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00449458242294044</v>
+        <v>0.005982800716697907</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2892307453017128</v>
+        <v>0.2889210511748294</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1489475395419449</v>
+        <v>0.152598570159998</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.002701067786354705</v>
+        <v>-0.01016665043107534</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5811625583897804</v>
+        <v>0.5880087527807341</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05215772885054237</v>
+        <v>0.05831260422500194</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.007179536710967835</v>
+        <v>-0.005957694933862298</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1192006927970662</v>
+        <v>0.1146433802895679</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2408086015254406</v>
+        <v>-0.2306545913673445</v>
       </c>
       <c r="E5" t="n">
-        <v>0.226449528103505</v>
+        <v>0.2187392014996199</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9519719248057356</v>
+        <v>0.9585548324340626</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.254199727392546</v>
+        <v>0.2614273190347502</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1359741503568106</v>
+        <v>0.1392840286028361</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.01230471013523698</v>
+        <v>-0.01156436064845523</v>
       </c>
       <c r="E6" t="n">
-        <v>0.520704164920329</v>
+        <v>0.5344189987179557</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06155731817174591</v>
+        <v>0.06052675630474041</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.01736207699116157</v>
+        <v>-0.01841397076183377</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1252584178880409</v>
+        <v>0.1223193367586619</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2628640648121894</v>
+        <v>-0.2581554654216375</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2281399108298663</v>
+        <v>0.22132752389797</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8897582922382908</v>
+        <v>0.8803384800164815</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2130516308866099</v>
+        <v>0.1905247839024715</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1304889443384701</v>
+        <v>0.1312065100950982</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.04270200039744329</v>
+        <v>-0.06663525042111201</v>
       </c>
       <c r="E8" t="n">
-        <v>0.468805262170663</v>
+        <v>0.447684818226055</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1025283478824757</v>
+        <v>0.1464742032871106</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.156721727199001</v>
+        <v>0.164771970074634</v>
       </c>
       <c r="C9" t="n">
-        <v>0.117737409245161</v>
+        <v>0.1133318732696421</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.07403935455456773</v>
+        <v>-0.05735441983432213</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3874828089525697</v>
+        <v>0.3868983599835901</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1831520243955451</v>
+        <v>0.1459770678884139</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.1883785887128817</v>
+        <v>-0.2220479403681949</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1735423469866709</v>
+        <v>0.1738904480020738</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5285153385993098</v>
+        <v>-0.5628669557077944</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1517581611735464</v>
+        <v>0.1187710749714047</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2777044187344494</v>
+        <v>0.2016228791937935</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0209065662025417</v>
+        <v>0.03288756718509721</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1743778197312067</v>
+        <v>0.1776097727247111</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3208676801732415</v>
+        <v>-0.3152211906576809</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3626808125783249</v>
+        <v>0.3809963250278754</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9045684263639905</v>
+        <v>0.8530976171323728</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.03334522471451092</v>
+        <v>-0.01926300923725728</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1860364989866872</v>
+        <v>0.1857937530359851</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3979700625383401</v>
+        <v>-0.3834120737403174</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3312796131093183</v>
+        <v>0.3448860552658028</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8577490768611493</v>
+        <v>0.9174236707386755</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01086453625941078</v>
+        <v>0.02751012339829566</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1602845263126507</v>
+        <v>0.1635058900678624</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3032873625924472</v>
+        <v>-0.2929555323948799</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3250164351112687</v>
+        <v>0.3479757791914713</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9459585246097266</v>
+        <v>0.8663853688450225</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.233037473710975</v>
+        <v>-0.2140509916498262</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2012003069444301</v>
+        <v>0.1996415110470125</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.6273828290004622</v>
+        <v>-0.6053411631211262</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1613078815785121</v>
+        <v>0.1772391798214737</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2467676699300563</v>
+        <v>0.2836406395758073</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.09965455462652113</v>
+        <v>0.1171045186779468</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1656732526425071</v>
+        <v>0.1619967599285946</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2250590537543981</v>
+        <v>-0.2004032963942801</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4243681630074403</v>
+        <v>0.4346123337501737</v>
       </c>
       <c r="F15" t="n">
-        <v>0.54749859929547</v>
+        <v>0.4697524708434641</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.01874536226599183</v>
+        <v>-0.01272868241196959</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1565440021404979</v>
+        <v>0.1645558921490834</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3255659684571288</v>
+        <v>-0.3352523044680306</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2880752439251451</v>
+        <v>0.3097949396440914</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9046851482627974</v>
+        <v>0.9383437421023132</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.04233870019822498</v>
+        <v>-0.04675708148500221</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1758724946603598</v>
+        <v>0.1760312745689466</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3870424556037432</v>
+        <v>-0.391772039792819</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3023650552072932</v>
+        <v>0.2982578768228147</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8097603553698299</v>
+        <v>0.7905333934586954</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.0388956425480854</v>
+        <v>-0.02301946934380645</v>
       </c>
       <c r="C18" t="n">
-        <v>0.172341155018485</v>
+        <v>0.1644652153812266</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3766780994383504</v>
+        <v>-0.3453653682006335</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2988868143421796</v>
+        <v>0.2993264295130206</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8214426839931814</v>
+        <v>0.8886871854160935</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.2259643334332908</v>
+        <v>-0.2146921070890924</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1649619987438162</v>
+        <v>0.1515530665957192</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5492839097889122</v>
+        <v>-0.5117306593633023</v>
       </c>
       <c r="E19" t="n">
-        <v>0.09735524292233072</v>
+        <v>0.0823464451851175</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1707505013344383</v>
+        <v>0.1565959844710089</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.001856045673099274</v>
+        <v>-0.005402522655628015</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1697988822073226</v>
+        <v>0.1655922621823109</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3346557394146106</v>
+        <v>-0.3299573926514713</v>
       </c>
       <c r="E20" t="n">
-        <v>0.330943648068412</v>
+        <v>0.3191523473402153</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9912786192860347</v>
+        <v>0.973973271646224</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.2694360050173388</v>
+        <v>-0.2427296873564388</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1706795908025512</v>
+        <v>0.1660896874446662</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6039618558863731</v>
+        <v>-0.5682594929514989</v>
       </c>
       <c r="E21" t="n">
-        <v>0.06508984585169547</v>
+        <v>0.08280011823862124</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1144262170121916</v>
+        <v>0.1438954327129222</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.04330756237050019</v>
+        <v>-0.03768411407691213</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1787654308239331</v>
+        <v>0.1797730666913064</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3936813684661956</v>
+        <v>-0.3900328501821898</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3070662437251951</v>
+        <v>0.3146646220283655</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8085793600983576</v>
+        <v>0.8339639046817252</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.06881283838346799</v>
+        <v>-0.02464806102588252</v>
       </c>
       <c r="C23" t="n">
-        <v>0.197110549087503</v>
+        <v>0.1900831223009973</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4551424155678883</v>
+        <v>-0.3972041348047595</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3175167388009522</v>
+        <v>0.3479080127529945</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7270083496277238</v>
+        <v>0.8968275912688037</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.196954016243145</v>
+        <v>0.2059416113771989</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0937494824155654</v>
+        <v>0.09524738374795881</v>
       </c>
       <c r="D24" t="n">
-        <v>0.01320840713936575</v>
+        <v>0.01926016960953394</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3806996253469244</v>
+        <v>0.3926230531448638</v>
       </c>
       <c r="F24" t="n">
-        <v>0.03565374596865849</v>
+        <v>0.03060460934207491</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.03634889040649857</v>
+        <v>0.04452008568401996</v>
       </c>
       <c r="C25" t="n">
-        <v>0.07602907370981744</v>
+        <v>0.07833813972634324</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1126653558426847</v>
+        <v>-0.1090198467954792</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1853631366556818</v>
+        <v>0.1980600181635191</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6325847398491921</v>
+        <v>0.5698267649268591</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.05413145196454881</v>
+        <v>0.04831767222516927</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1043032330074431</v>
+        <v>0.1075095082429102</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.150299128201129</v>
+        <v>-0.1623970919265468</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2585620321302267</v>
+        <v>0.2590324363768854</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6037736178761517</v>
+        <v>0.6531236814450443</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.02253013030987348</v>
+        <v>0.01812015855057364</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1120586513646963</v>
+        <v>0.1120508625951184</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.1971007905210615</v>
+        <v>-0.2014954965725047</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2421610511408085</v>
+        <v>0.237735813673652</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8406543250742339</v>
+        <v>0.8715313227345125</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.03876556387984111</v>
+        <v>-0.04940558150093557</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1063567021845979</v>
+        <v>0.1079780618094177</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2472208696761055</v>
+        <v>-0.2610386937678342</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1696897419164232</v>
+        <v>0.162227530765963</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7154948810826502</v>
+        <v>0.6472743129266677</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0505793121373093</v>
+        <v>0.04280137104231072</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1019815536749181</v>
+        <v>0.1082244098992595</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1493008601529686</v>
+        <v>-0.1693145746083381</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2504594844275872</v>
+        <v>0.2549173166929595</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6199188913105707</v>
+        <v>0.6924833512519126</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.4119396667161183</v>
+        <v>0.4119231277135925</v>
       </c>
       <c r="C30" t="n">
-        <v>0.03659672575618315</v>
+        <v>0.03551662021466755</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3402114022819099</v>
+        <v>0.3423118312402568</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4836679311503267</v>
+        <v>0.4815344241869281</v>
       </c>
       <c r="F30" t="n">
-        <v>2.158943053597389e-29</v>
+        <v>4.216315028049169e-31</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.002530268399225321</v>
+        <v>-0.02794494020865268</v>
       </c>
       <c r="C31" t="n">
-        <v>0.005622270861038281</v>
+        <v>0.01461262990600822</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.008489179999738708</v>
+        <v>-0.05658516854384171</v>
       </c>
       <c r="E31" t="n">
-        <v>0.01354971679818935</v>
+        <v>0.0006952881265363427</v>
       </c>
       <c r="F31" t="n">
-        <v>0.652678825856178</v>
+        <v>0.0558271290415045</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.4629205333279597</v>
+        <v>0.007976972803062372</v>
       </c>
       <c r="C32" t="n">
-        <v>0.04621294014466904</v>
+        <v>0.004378059075285191</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3723448350247032</v>
+        <v>-0.0006038653066853337</v>
       </c>
       <c r="E32" t="n">
-        <v>0.5534962316312163</v>
+        <v>0.01655781091281008</v>
       </c>
       <c r="F32" t="n">
-        <v>1.281847010006495e-23</v>
+        <v>0.06844981601298381</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.005527031905797136</v>
+        <v>0.4575134647665859</v>
       </c>
       <c r="C33" t="n">
-        <v>0.004785353131548166</v>
+        <v>0.04666760652833873</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.01490615169693751</v>
+        <v>0.3660466367263557</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003852087885343234</v>
+        <v>0.5489802928068162</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2480947874864714</v>
+        <v>1.085758088206482e-22</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2264,19 +2264,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.01007955802610835</v>
+        <v>-0.01025948591986665</v>
       </c>
       <c r="C34" t="n">
-        <v>0.005481376984073869</v>
+        <v>0.005466797757691314</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.02082285950057992</v>
+        <v>-0.02097421263570595</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0006637434483632142</v>
+        <v>0.0004552407959726532</v>
       </c>
       <c r="F34" t="n">
-        <v>0.06593381725815285</v>
+        <v>0.06056056299802851</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.459245807259868</v>
+        <v>-0.005696864427362675</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1749577793479938</v>
+        <v>0.005018673731113935</v>
       </c>
       <c r="D35" t="n">
-        <v>1.116334860922694</v>
+        <v>-0.01553328419050324</v>
       </c>
       <c r="E35" t="n">
-        <v>1.802156753597041</v>
+        <v>0.004139555335777892</v>
       </c>
       <c r="F35" t="n">
-        <v>7.393970872040787e-17</v>
+        <v>0.2563194081069062</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2310,23 +2310,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.0131555362432474</v>
+        <v>1.440174177203154</v>
       </c>
       <c r="C36" t="n">
-        <v>0.01499399752296756</v>
+        <v>0.1799506899318459</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0425432313725466</v>
+        <v>1.087477305943602</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0162321588860518</v>
+        <v>1.792871048462707</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3802765536663507</v>
+        <v>1.212661290945629e-15</v>
       </c>
       <c r="G36" t="n">
         <v>0.05</v>
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.350970771285248</v>
+        <v>-2.68060017980294</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4605522587714034</v>
+        <v>0.4771933030981267</v>
       </c>
       <c r="D2" t="n">
-        <v>3.313590542287848e-07</v>
+        <v>1.93818176827037e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2391,13 +2391,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02128055977478192</v>
+        <v>-0.02542074333516159</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09751395156308111</v>
+        <v>0.1002143663033998</v>
       </c>
       <c r="D3" t="n">
-        <v>0.827249191641336</v>
+        <v>0.7997554080121703</v>
       </c>
     </row>
     <row r="4">
@@ -2407,13 +2407,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2245966634275915</v>
+        <v>0.2244463748843408</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2329354389845562</v>
+        <v>0.2335027157442914</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3349449904957182</v>
+        <v>0.3364439424069164</v>
       </c>
     </row>
     <row r="5">
@@ -2423,13 +2423,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8167052829997485</v>
+        <v>0.8155080917228588</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1617156577703267</v>
+        <v>0.173402651392118</v>
       </c>
       <c r="D5" t="n">
-        <v>4.412210487480358e-07</v>
+        <v>2.563995828054386e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2439,13 +2439,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03599538577094948</v>
+        <v>0.03527526670387294</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1898688322218615</v>
+        <v>0.1916882946919544</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8496380437366924</v>
+        <v>0.8539945454713553</v>
       </c>
     </row>
     <row r="7">
@@ -2455,13 +2455,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2765708211818085</v>
+        <v>0.2773648159307716</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1824472225347018</v>
+        <v>0.1901447102133385</v>
       </c>
       <c r="D7" t="n">
-        <v>0.129545920374235</v>
+        <v>0.1446466431125523</v>
       </c>
     </row>
     <row r="8">
@@ -2471,13 +2471,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1102648615599912</v>
+        <v>0.1036811851537241</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1853641405651108</v>
+        <v>0.1952515666982444</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5519401263365121</v>
+        <v>0.5954095400432468</v>
       </c>
     </row>
     <row r="9">
@@ -2487,13 +2487,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8745743640527194</v>
+        <v>0.8738774480300985</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1615402513662274</v>
+        <v>0.1695280942409136</v>
       </c>
       <c r="D9" t="n">
-        <v>6.164188141358052e-08</v>
+        <v>2.539495077342719e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.04349724922704642</v>
+        <v>-0.04456520772617057</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2655215602978132</v>
+        <v>0.2604021031716314</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8698743077153893</v>
+        <v>0.8641137091517844</v>
       </c>
     </row>
     <row r="11">
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2685655156863916</v>
+        <v>-0.2737623724798145</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2761865361461748</v>
+        <v>0.2787881385465063</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3308484806726052</v>
+        <v>0.3261132423877634</v>
       </c>
     </row>
     <row r="12">
@@ -2535,13 +2535,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08406558527820192</v>
+        <v>0.08100487957118158</v>
       </c>
       <c r="C12" t="n">
-        <v>0.251020166800007</v>
+        <v>0.2596429772097172</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7377037334343584</v>
+        <v>0.7550514391424689</v>
       </c>
     </row>
     <row r="13">
@@ -2551,13 +2551,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04159103469582721</v>
+        <v>0.03917827337461771</v>
       </c>
       <c r="C13" t="n">
-        <v>0.255561465250315</v>
+        <v>0.2572958805743772</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8707201879025983</v>
+        <v>0.8789745077123736</v>
       </c>
     </row>
     <row r="14">
@@ -2567,13 +2567,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05097157642059893</v>
+        <v>-0.05296103812307912</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2615504699624188</v>
+        <v>0.2610089865588722</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8454850334004391</v>
+        <v>0.8392062624375538</v>
       </c>
     </row>
     <row r="15">
@@ -2583,13 +2583,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1235593461635321</v>
+        <v>0.1181322726534163</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2569613848518211</v>
+        <v>0.2572294350577189</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6306245929938302</v>
+        <v>0.6460556128984085</v>
       </c>
     </row>
     <row r="16">
@@ -2599,13 +2599,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.002490750131026257</v>
+        <v>-0.00400098624037939</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2457746491930773</v>
+        <v>0.2383903410311194</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9919141495524532</v>
+        <v>0.9866094604655136</v>
       </c>
     </row>
     <row r="17">
@@ -2615,13 +2615,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1110262478895003</v>
+        <v>0.1057185310395308</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2594324060220158</v>
+        <v>0.2543340222421757</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6686814903924607</v>
+        <v>0.6776529122567302</v>
       </c>
     </row>
     <row r="18">
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1338440250599403</v>
+        <v>-0.1377694895733253</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2694490717592011</v>
+        <v>0.2636874203313639</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6193779257550096</v>
+        <v>0.6013412201546287</v>
       </c>
     </row>
     <row r="19">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02068301206114321</v>
+        <v>-0.0255715409422322</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2629683391871477</v>
+        <v>0.2527597901538112</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9373093461992266</v>
+        <v>0.9194160355966682</v>
       </c>
     </row>
     <row r="20">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.0686991433762508</v>
+        <v>-0.07344622569376394</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2617458461247386</v>
+        <v>0.2674578609541013</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7929629071620667</v>
+        <v>0.7836169672222786</v>
       </c>
     </row>
     <row r="21">
@@ -2679,13 +2679,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2112158738988716</v>
+        <v>0.2063167170305062</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2400889859196068</v>
+        <v>0.2442896532450728</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3790001987958982</v>
+        <v>0.3983578134719856</v>
       </c>
     </row>
     <row r="22">
@@ -2695,13 +2695,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.159933319308369</v>
+        <v>-0.1704634573362025</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2649283257747139</v>
+        <v>0.2696748454965907</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5460529306471213</v>
+        <v>0.5273167196806369</v>
       </c>
     </row>
     <row r="23">
@@ -2711,13 +2711,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.4920005620651325</v>
+        <v>-0.5008110927334755</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2884409459397611</v>
+        <v>0.2870672180445716</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08805953197431808</v>
+        <v>0.08105838975171867</v>
       </c>
     </row>
     <row r="24">
@@ -2727,13 +2727,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9425285809878476</v>
+        <v>0.9366864721074269</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1559773650465781</v>
+        <v>0.1483430409733375</v>
       </c>
       <c r="D24" t="n">
-        <v>1.515312581506736e-09</v>
+        <v>2.713396260923871e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5768512495314141</v>
+        <v>-0.5776106069409676</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1130405709043027</v>
+        <v>0.1143619392421805</v>
       </c>
       <c r="D25" t="n">
-        <v>3.342294640071132e-07</v>
+        <v>4.401383208103756e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2759,13 +2759,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2384858887162336</v>
+        <v>0.2373161448441742</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1457315480836286</v>
+        <v>0.1503781926377478</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1017404238903948</v>
+        <v>0.1145360411757809</v>
       </c>
     </row>
     <row r="27">
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04585234373593617</v>
+        <v>-0.04350476117998649</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1593109532353293</v>
+        <v>0.1611879340386415</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7734870970055308</v>
+        <v>0.7872365295400219</v>
       </c>
     </row>
     <row r="28">
@@ -2791,13 +2791,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07857740431296747</v>
+        <v>-0.07514354096975731</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1565335672967476</v>
+        <v>0.1613683918223567</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6156785148897228</v>
+        <v>0.6414556246120153</v>
       </c>
     </row>
     <row r="29">
@@ -2807,45 +2807,45 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09755305493394664</v>
+        <v>0.09749293462742098</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1499487653516257</v>
+        <v>0.1543265796290168</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5153202832397639</v>
+        <v>0.5275624553510017</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.006860378637723895</v>
+        <v>-0.004129656026475424</v>
       </c>
       <c r="C30" t="n">
-        <v>0.006945236405256705</v>
+        <v>0.02222260881033181</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3232594861617505</v>
+        <v>0.8525770672961283</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.002646425713821547</v>
+        <v>0.006335499136474501</v>
       </c>
       <c r="C31" t="n">
-        <v>0.007095424075339026</v>
+        <v>0.006871422968197188</v>
       </c>
       <c r="D31" t="n">
-        <v>0.7091660102282209</v>
+        <v>0.3565249957666434</v>
       </c>
     </row>
     <row r="32">
@@ -2855,45 +2855,45 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.004895000819746557</v>
+        <v>-0.005012017390962181</v>
       </c>
       <c r="C32" t="n">
-        <v>0.008684655396149939</v>
+        <v>0.008304876992454852</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5730005966817302</v>
+        <v>0.5461741835341496</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.2261835420647834</v>
+        <v>-0.00241813341219285</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1139281184793711</v>
+        <v>0.007135781003458538</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04710910483736543</v>
+        <v>0.7347043603418298</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.01540023496026497</v>
+        <v>0.2280638724458788</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0213723694247541</v>
+        <v>0.1146565719927948</v>
       </c>
       <c r="D34" t="n">
-        <v>0.47117565131408</v>
+        <v>0.04668969945129902</v>
       </c>
     </row>
   </sheetData>
